--- a/结果提交表_D题.xlsx
+++ b/结果提交表_D题.xlsx
@@ -9270,14 +9270,14 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>S001;S002;S003;S004;S005;S006;S007;S008;S009;S011;S012;S013;S015</t>
+          <t>S001;S002;S003;S004;S005;S006;S007;S008;S009;S010;S011;S012;S014;S015</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>2</v>
@@ -9286,7 +9286,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>4</v>
@@ -9312,14 +9312,14 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>S010;S014</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -9328,16 +9328,16 @@
         <v>1</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
@@ -9354,14 +9354,14 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>S001;S002;S003;S004;S005;S006;S007;S008;S009;S011;S012;S015</t>
+          <t>S001;S003;S004;S005;S006;S007;S008;S009;S010;S011;S012;S014;S015</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>2</v>
@@ -9370,10 +9370,10 @@
         <v>3</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2</v>
@@ -9396,32 +9396,32 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>S010;S014</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
@@ -9460,10 +9460,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>

--- a/结果提交表_D题.xlsx
+++ b/结果提交表_D题.xlsx
@@ -15,10 +15,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Q1_单点组批'!$A$1:$I$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q2_运输架次'!$A$1:$H$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q2_运输架次'!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Q2_逐箱交付'!$A$1:$D$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Q3_中继架次'!$A$1:$K$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Q3_通信保障'!$A$1:$F$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Q3_中继架次'!$A$1:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Q3_通信保障'!$A$1:$F$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Q4_分区配置'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -1638,13 +1638,13 @@
         <v>0.129</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1889.225246196556</v>
+        <v>1907.482106548119</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>3.403284468190999</v>
+        <v>3.410376019243793</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>57.45894414761251</v>
+        <v>57.37029975945258</v>
       </c>
     </row>
     <row r="12">
@@ -1786,13 +1786,13 @@
         <v>0.067</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1186.67880728014</v>
+        <v>1189.630805164254</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1.07596581372392</v>
+        <v>1.077146139786049</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>73.10085465690199</v>
+        <v>73.07134650534877</v>
       </c>
     </row>
     <row r="16">
@@ -1955,7 +1955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
     <col width="12" customWidth="1" style="3" min="1" max="2"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1297.426742579472</v>
+        <v>1561.426742579472</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>2.026190285785253</v>
+        <v>2.926237396999126</v>
       </c>
     </row>
     <row r="3">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1847.008137577008</v>
+        <v>2111.008137577008</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4.78619765254977</v>
+        <v>6.300716422874222</v>
       </c>
     </row>
     <row r="4">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1712.442685777107</v>
+        <v>1727.318646063566</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.899018130953899</v>
+        <v>1.905042879413254</v>
       </c>
     </row>
     <row r="6">
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1863.801424717148</v>
+        <v>1923.801424717148</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.471728045873088</v>
+        <v>2.755193534285018</v>
       </c>
     </row>
     <row r="8">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1808.598451895563</v>
+        <v>1868.598451895563</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.922188491244238</v>
+        <v>2.137232728134707</v>
       </c>
     </row>
     <row r="10">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1297.426742579472</v>
+        <v>1561.426742579472</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3469.237620798425</v>
+        <v>3997.237620798425</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.794541363919091</v>
+        <v>6.322211453981215</v>
       </c>
     </row>
     <row r="11">
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1808.598451895563</v>
+        <v>1868.598451895563</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3578.172565165816</v>
+        <v>3698.172565165815</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.073819419783548</v>
+        <v>2.310845764235462</v>
       </c>
     </row>
     <row r="14">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1863.801424717148</v>
+        <v>1923.801424717148</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3382.826745665397</v>
+        <v>3502.826745665397</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.778276884886143</v>
+        <v>1.981238950041894</v>
       </c>
     </row>
     <row r="15">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1847.008137577008</v>
+        <v>2111.008137577008</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3427.91423805303</v>
+        <v>3757.91423805303</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.690842687599887</v>
+        <v>3.780634511364007</v>
       </c>
     </row>
     <row r="16">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3411.515253627319</v>
+        <v>3414.467251511433</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.154269843001951</v>
+        <v>1.155465399077785</v>
       </c>
     </row>
     <row r="17">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3427.91423805303</v>
+        <v>3757.91423805303</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4923.340980632502</v>
+        <v>5385.340980632503</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.621056380285868</v>
+        <v>3.004662065601599</v>
       </c>
     </row>
     <row r="18">
@@ -2608,18 +2608,18 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3976.603335142571</v>
+        <v>4650.785502105443</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S006;S007</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5472.030077722043</v>
+        <v>7064.564917981724</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.672672533456055</v>
+        <v>4.288061981831905</v>
       </c>
     </row>
     <row r="19">
@@ -2630,21 +2630,21 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5260.850799278</v>
+        <v>3502.826745665397</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>7371.858936855007</v>
+        <v>5262.716798525608</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>6.124988496916554</v>
+        <v>2.368626232681691</v>
       </c>
     </row>
     <row r="20">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2676,22 +2676,22 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5601.092573526512</v>
+        <v>5615.169418214115</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>S006;S007</t>
+          <t>S011;S004</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>8005.743559227012</v>
+        <v>8108.812464039185</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4.285379625670703</v>
+        <v>5.846544590465472</v>
       </c>
     </row>
     <row r="21">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2716,18 +2716,18 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>7371.858936855007</v>
+        <v>7064.564917981724</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S005;S008</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>9807.669815073959</v>
+        <v>9643.106358378987</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.147682578627633</v>
+        <v>6.319205968676798</v>
       </c>
     </row>
     <row r="22">
@@ -2738,32 +2738,32 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>8005.743559227012</v>
+        <v>2677.586124530284</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S013;S010</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>10178.92905160478</v>
+        <v>4687.579586128566</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5.539956843832735</v>
+        <v>2.246365960902664</v>
       </c>
     </row>
     <row r="23">
@@ -2774,180 +2774,36 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>9864.043321436571</v>
+        <v>3784.385289573988</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>S008;S015</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>12695.76319363104</v>
+        <v>5804.628121731744</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>6.317750383984248</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>U03</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>A-BAT-04</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>2677.586124530284</v>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>S009;S012</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>5053.632567273051</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>3.161452104856824</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>U05</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>B-BAT-02</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>3382.826745665397</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>S010;S014</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>5438.230095642923</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>2.06433908390128</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>U02</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>A-BAT-02</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>3411.515253627319</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>S013</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>4963.539769535888</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1.871010430651815</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>U07</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>C-BAT-03</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>10178.92905160478</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>S011;S005</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>12286.98258465523</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>4.068074912724184</v>
+        <v>2.423407135490848</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H27"/>
+  <autoFilter ref="A1:H23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3006,7 +2862,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>912.898371289736</v>
+        <v>1032.898371289736</v>
       </c>
     </row>
     <row r="3">
@@ -3026,7 +2882,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>948.898371289736</v>
+        <v>1068.898371289736</v>
       </c>
     </row>
     <row r="4">
@@ -3046,1547 +2902,1547 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>984.898371289736</v>
+        <v>1104.898371289736</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>S002-MED-01</t>
+          <t>S001-WAT-02</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1188.914068788504</v>
+        <v>1140.898371289736</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>S002-WAT-01</t>
+          <t>S001-WAT-03</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1224.914068788504</v>
+        <v>1176.898371289736</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>S006-MED-01</t>
+          <t>S001-WAT-04</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>905.071191714371</v>
+        <v>1212.898371289736</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>S006-WAT-01</t>
+          <t>S001-WAT-05</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T001</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>935.071191714371</v>
+        <v>1248.898371289736</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>S007-MED-01</t>
+          <t>S002-MED-01</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1103.861342888554</v>
+        <v>1308.914068788504</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>S007-WAT-01</t>
+          <t>S002-WAT-01</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>T004</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1133.861342888554</v>
+        <v>1344.914068788504</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>S010-MED-01</t>
+          <t>S002-WAT-02</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1074.4634536137</v>
+        <v>1380.914068788504</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>S010-WAT-01</t>
+          <t>S002-WAT-03</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>T005</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1104.4634536137</v>
+        <v>1416.914068788504</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>S012-MED-01</t>
+          <t>S002-WAT-04</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1181.830712358574</v>
+        <v>1452.914068788504</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>S012-WAT-01</t>
+          <t>S002-FOD-01</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>T006</t>
+          <t>T002</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1211.830712358574</v>
+        <v>1488.914068788504</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>S013-MED-01</t>
+          <t>S006-MED-01</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1053.545591287618</v>
+        <v>905.071191714371</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>S013-WAT-01</t>
+          <t>S006-WAT-01</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>T007</t>
+          <t>T003</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1083.545591287618</v>
+        <v>935.071191714371</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>S014-MED-01</t>
+          <t>S007-MED-01</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1151.855892614448</v>
+        <v>1111.299323031783</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>S014-WAT-01</t>
+          <t>S007-WAT-01</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>T008</t>
+          <t>T004</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1181.855892614448</v>
+        <v>1141.299323031783</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>S003-MED-01</t>
+          <t>S010-MED-01</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2642.792181688949</v>
+        <v>1074.4634536137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>S003-WAT-01</t>
+          <t>S010-WAT-01</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>T009</t>
+          <t>T005</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2678.792181688949</v>
+        <v>1104.4634536137</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>S004-MED-01</t>
+          <t>S012-MED-01</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2656.242976046436</v>
+        <v>1211.830712358574</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>S004-WAT-01</t>
+          <t>S012-WAT-01</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>T010</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2686.242976046436</v>
+        <v>1241.830712358574</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>S008-MED-01</t>
+          <t>S012-FOD-01</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T006</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2950.354128491676</v>
+        <v>1271.830712358574</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>S008-WAT-01</t>
+          <t>S013-MED-01</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>T011</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2980.354128491676</v>
+        <v>1053.545591287618</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>S015-MED-01</t>
+          <t>S013-WAT-01</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T007</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2936.825508530689</v>
+        <v>1083.545591287618</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>S015-WAT-01</t>
+          <t>S014-MED-01</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>T012</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2966.825508530689</v>
+        <v>1181.855892614448</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>S005-MED-01</t>
+          <t>S014-WAT-01</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2876.070751857939</v>
+        <v>1211.855892614448</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>S005-WAT-01</t>
+          <t>S014-FOD-01</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>T013</t>
+          <t>T008</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2906.070751857939</v>
+        <v>1241.855892614448</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>S009-MED-01</t>
+          <t>S003-MED-01</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2902.346187815019</v>
+        <v>3026.792181688949</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>S009-WAT-01</t>
+          <t>S003-WAT-01</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>T014</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2938.346187815019</v>
+        <v>3062.792181688949</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>S011-MED-01</t>
+          <t>S003-WAT-02</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3053.409987826418</v>
+        <v>3098.792181688949</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>S011-WAT-01</t>
+          <t>S003-WAT-03</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>T015</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3083.409987826418</v>
+        <v>3134.792181688949</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>S001-WAT-02</t>
+          <t>S003-WAT-04</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4430.812609342765</v>
+        <v>3170.792181688949</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>S001-WAT-03</t>
+          <t>S003-FOD-01</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T009</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4466.812609342765</v>
+        <v>3206.792181688949</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>S001-WAT-04</t>
+          <t>S004-MED-01</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4502.812609342765</v>
+        <v>2656.242976046436</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>S001-FOD-01</t>
+          <t>S004-WAT-01</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T010</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>4538.812609342765</v>
+        <v>2686.242976046436</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>S001-FOD-02</t>
+          <t>S008-MED-01</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>4574.812609342765</v>
+        <v>2950.354128491676</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>S001-FOD-03</t>
+          <t>S008-WAT-01</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>T016</t>
+          <t>T011</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>4610.812609342765</v>
+        <v>2980.354128491676</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>S001-WAT-05</t>
+          <t>S015-MED-01</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>4979.501706432306</v>
+        <v>3026.825508530689</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>S001-WAT-06</t>
+          <t>S015-WAT-01</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>5015.501706432306</v>
+        <v>3056.825508530689</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>S001-WAT-07</t>
+          <t>S015-FOD-01</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T012</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>5051.501706432306</v>
+        <v>3086.825508530689</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>S001-WAT-08</t>
+          <t>S005-MED-01</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>5087.501706432306</v>
+        <v>2966.070751857939</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>S001-HYG-01</t>
+          <t>S005-WAT-01</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>5123.501706432306</v>
+        <v>2996.070751857939</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>S001-HYG-02</t>
+          <t>S005-FOD-01</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>T017</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>5159.501706432306</v>
+        <v>3026.070751857939</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>S002-WAT-02</t>
+          <t>S009-MED-01</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>6569.764868066503</v>
+        <v>3196.346187815019</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>S002-WAT-03</t>
+          <t>S009-WAT-01</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>6605.764868066503</v>
+        <v>3232.346187815019</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>S002-WAT-04</t>
+          <t>S009-FOD-01</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T014</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>6641.764868066503</v>
+        <v>3268.346187815019</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>S002-FOD-01</t>
+          <t>S011-MED-01</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>6677.764868066503</v>
+        <v>3054.885986768475</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>S002-FOD-02</t>
+          <t>S011-WAT-01</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T015</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>6713.764868066503</v>
+        <v>3084.885986768475</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>S002-HYG-01</t>
+          <t>S001-WAT-06</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>6749.764868066503</v>
+        <v>4820.812609342766</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>S006-WAT-02</t>
+          <t>S001-WAT-07</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>6660.169516562722</v>
+        <v>4856.812609342766</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>S006-WAT-03</t>
+          <t>S001-WAT-08</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>6696.169516562722</v>
+        <v>4892.812609342766</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>S006-FOD-01</t>
+          <t>S001-FOD-01</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>6732.169516562722</v>
+        <v>4928.812609342766</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>S006-HYG-01</t>
+          <t>S001-FOD-02</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>6768.169516562722</v>
+        <v>4964.812609342766</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>S007-WAT-02</t>
+          <t>S001-FOD-03</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>7383.090936128734</v>
+        <v>5000.812609342766</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>S007-FOD-01</t>
+          <t>S001-HYG-01</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>7419.090936128734</v>
+        <v>5036.812609342766</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>S007-HYG-01</t>
+          <t>S001-HYG-02</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T016</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>7455.090936128734</v>
+        <v>5072.812609342766</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>S003-WAT-02</t>
+          <t>S006-WAT-02</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>8837.224375964484</v>
+        <v>5709.862445141654</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>S003-WAT-03</t>
+          <t>S006-WAT-03</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>8873.224375964484</v>
+        <v>5745.862445141654</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>S003-WAT-04</t>
+          <t>S006-FOD-01</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>8909.224375964484</v>
+        <v>5781.862445141654</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>S003-FOD-01</t>
+          <t>S006-HYG-01</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>8945.224375964484</v>
+        <v>5817.862445141654</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>S003-FOD-02</t>
+          <t>S007-WAT-02</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>8981.224375964484</v>
+        <v>6432.783864707664</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>S003-HYG-01</t>
+          <t>S007-FOD-01</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>9017.224375964484</v>
+        <v>6468.783864707664</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>S004-WAT-02</t>
+          <t>S007-HYG-01</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>9351.306305415894</v>
+        <v>6504.783864707664</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>S004-WAT-03</t>
+          <t>S002-FOD-02</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D65" s="4" t="n">
-        <v>9387.306305415894</v>
+        <v>4634.711772095503</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>S004-FOD-01</t>
+          <t>S002-HYG-01</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>9423.306305415894</v>
+        <v>4664.711772095503</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>S004-HYG-01</t>
+          <t>S011-FOD-01</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>9459.306305415894</v>
+        <v>6577.675113358091</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>S008-WAT-02</t>
+          <t>S004-WAT-02</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>11189.76326894935</v>
+        <v>7281.189717850304</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>S008-FOD-01</t>
+          <t>S004-WAT-03</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
-        <v>11225.76326894935</v>
+        <v>7317.189717850304</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>S008-HYG-01</t>
+          <t>S004-FOD-01</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>11261.76326894935</v>
+        <v>7353.189717850304</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>S015-FOD-01</t>
+          <t>S004-HYG-01</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>T022</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>12033.51959443407</v>
+        <v>7389.189717850304</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>S009-FOD-01</t>
+          <t>S005-WAT-02</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>3774.944029989337</v>
+        <v>8259.222726567827</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>S012-FOD-01</t>
+          <t>S005-WAT-03</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>T023</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D73" s="4" t="n">
-        <v>4278.354359218226</v>
+        <v>8295.222726567827</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>S010-FOD-01</t>
+          <t>S005-HYG-01</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>T024</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>4377.649533784222</v>
+        <v>8331.222726567827</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>S014-FOD-01</t>
+          <t>S008-WAT-02</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>T024</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>4811.487536361808</v>
+        <v>8867.066410866213</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>S013-FOD-01</t>
+          <t>S008-FOD-01</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>T025</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>4435.060844914937</v>
+        <v>8903.066410866213</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>S011-FOD-01</t>
+          <t>S008-HYG-01</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>11139.62329350168</v>
+        <v>8939.066410866213</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>S005-WAT-02</t>
+          <t>S013-FOD-01</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>11673.59477606913</v>
+        <v>3731.131715817902</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>S005-WAT-03</t>
+          <t>S010-FOD-01</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T021</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
-        <v>11709.59477606913</v>
+        <v>4138.1894658482</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>S005-FOD-01</t>
+          <t>S003-FOD-02</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>11745.59477606913</v>
+        <v>5042.480038986199</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>S005-HYG-01</t>
+          <t>S003-HYG-01</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>T026</t>
+          <t>T022</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>11781.59477606913</v>
+        <v>5072.480038986199</v>
       </c>
     </row>
   </sheetData>
@@ -4704,13 +4560,13 @@
         <v>720.1745637686945</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>2223.975988485842</v>
+        <v>2471.182701345702</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2777.633727913716</v>
+        <v>3024.840440773577</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.7576570360930388</v>
+        <v>0.8331924205779961</v>
       </c>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
@@ -4733,7 +4589,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0</v>
+        <v>153.3655747200519</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>109.2227777777778</v>
@@ -4745,16 +4601,16 @@
         <v>587.5166015625</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>566.8089890486426</v>
+        <v>720.1745637686945</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2223.975988485842</v>
+        <v>2471.182701345702</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2619.103027664692</v>
+        <v>2866.309740524553</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.7109241888700586</v>
+        <v>0.7395978699683334</v>
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
@@ -4777,7 +4633,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3077.633727913716</v>
+        <v>3324.840440773577</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>109.2055555555556</v>
@@ -4789,16 +4645,16 @@
         <v>703.3844604492188</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3780.646670135168</v>
+        <v>4027.853382995028</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>5604.607855370554</v>
+        <v>6103.664261213982</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>6145.59450262944</v>
+        <v>6644.650908472869</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.8407034802197859</v>
+        <v>0.9176575530758762</v>
       </c>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
@@ -4821,7 +4677,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2919.103027664692</v>
+        <v>3240.036676663482</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>109.2255555555556</v>
@@ -4833,16 +4689,16 @@
         <v>626.3524169921875</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3706.919733996238</v>
+        <v>4027.853382995028</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5604.607855370554</v>
+        <v>6103.664261213982</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>6223.978929784782</v>
+        <v>6723.03533562821</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.9228661017432478</v>
+        <v>0.9772924996679988</v>
       </c>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
@@ -4865,7 +4721,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6445.59450262944</v>
+        <v>6944.650908472869</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>109.2383333333333</v>
@@ -4877,16 +4733,16 @@
         <v>534.8773498535156</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7089.495449679997</v>
+        <v>7588.551855523426</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8310.401550156021</v>
+        <v>8875.457955999447</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>8778.233943027704</v>
+        <v>9343.290348871131</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.6306029137210614</v>
+        <v>0.6507695803877275</v>
       </c>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
@@ -4909,28 +4765,28 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9078.233943027704</v>
+        <v>9643.290348871131</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>109.2227777777778</v>
+        <v>109.2827777777778</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>23.04027777777777</v>
+        <v>23.02694444444445</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>587.5166015625</v>
+        <v>649.4981079101562</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>9645.042932076349</v>
+        <v>10363.46491263982</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>12547.98909708149</v>
+        <v>12267.24432851611</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>12943.11613626034</v>
+        <v>12820.90206794398</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.091578933904708</v>
+        <v>0.879872533391663</v>
       </c>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
@@ -4953,28 +4809,28 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6523.978929784782</v>
+        <v>9804.307051180182</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>109.2055555555556</v>
+        <v>109.2033333333333</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>23.04944444444444</v>
+        <v>23.02083333333333</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>703.3844604492188</v>
+        <v>689.1195983886719</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7226.991872006233</v>
+        <v>10363.46491263982</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>12547.98909708149</v>
+        <v>12267.24432851611</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>13088.97574434038</v>
+        <v>12663.18715650814</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.909242270170858</v>
+        <v>0.7741950893421772</v>
       </c>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
@@ -4997,28 +4853,28 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>13243.11613626034</v>
+        <v>13120.90206794398</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>109.2055555555556</v>
+        <v>109.2255555555556</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>23.04944444444444</v>
+        <v>23.06944444444445</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>703.3844604492188</v>
+        <v>626.3524169921875</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>13946.12907848179</v>
+        <v>13908.71877427553</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16192.60332889088</v>
+        <v>16042.3618201006</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16733.58997614976</v>
+        <v>16661.73289451483</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.9698046945784152</v>
+        <v>0.9949634397698676</v>
       </c>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
@@ -5032,37 +4888,37 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>R-PACK-03</t>
+          <t>R-PACK-02</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13388.97574434038</v>
+        <v>16961.73289451483</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>109.2255555555556</v>
+        <v>109.2827777777778</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>23.06944444444445</v>
+        <v>23.02694444444445</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>626.3524169921875</v>
+        <v>649.4981079101562</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>14176.79245067192</v>
+        <v>17681.90745828352</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>16192.60332889088</v>
+        <v>19900.44889868078</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>16811.97440330511</v>
+        <v>20454.10663810866</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.958959166334665</v>
+        <v>0.9760498186619636</v>
       </c>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
@@ -5076,16 +4932,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>R-PACK-02</t>
+          <t>R-PACK-03</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>17033.58997614976</v>
+        <v>16978.89451606207</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>109.2055555555556</v>
@@ -5097,16 +4953,16 @@
         <v>703.3844604492188</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>17736.60291837122</v>
+        <v>17681.90745828352</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>20311.51098183112</v>
+        <v>19900.44889868078</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>20852.49762909001</v>
+        <v>20441.43554593967</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.070159470788389</v>
+        <v>0.9612696692970264</v>
       </c>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
@@ -5120,126 +4976,70 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>R-PACK-04</t>
+          <t>R-PACK-01</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17111.97440330511</v>
+        <v>20754.10663810866</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>109.2255555555556</v>
+        <v>109.2055555555556</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>23.06944444444445</v>
+        <v>23.04944444444444</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>626.3524169921875</v>
+        <v>703.3844604492188</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17899.79110963665</v>
+        <v>21457.11958033012</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>20311.51098183112</v>
+        <v>23117.36241248787</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>20930.88205624535</v>
+        <v>23658.34905974676</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1.079931358938295</v>
+        <v>0.7906784278905102</v>
       </c>
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
       <c r="N12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>R-012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>R-PACK-01</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>21152.49762909001</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>109.2827777777778</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>23.02694444444445</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>649.4981079101562</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>21872.6721928587</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>23918.71863560147</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>24472.37637502934</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0.9233430138230888</v>
-      </c>
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>R-013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>R-PACK-03</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>21230.88205624535</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>109.2227777777778</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>23.04027777777777</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>587.5166015625</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>21797.69104529399</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>23918.71863560147</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>24313.84567478032</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.8526593694137543</v>
-      </c>
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
       <c r="N14" s="3" t="n"/>
@@ -5485,7 +5285,7 @@
       <c r="N29" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5496,7 +5296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W90"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" style="8" min="1" max="2"/>
@@ -5566,10 +5366,10 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>750.1745637686945</v>
+        <v>870.1745637686945</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1657.601306348167</v>
+        <v>1921.601306348166</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -5607,10 +5407,10 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>720.1745637686945</v>
+        <v>840.1745637686945</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1050.43259025649</v>
+        <v>1170.43259025649</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -5648,10 +5448,10 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1050.43259025649</v>
+        <v>1170.43259025649</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1858.799249442868</v>
+        <v>2122.799249442868</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -5693,10 +5493,10 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1858.799249442868</v>
+        <v>2122.799249442868</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2207.182701345702</v>
+        <v>2471.182701345702</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -5778,7 +5578,7 @@
         <v>720.1745637686945</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1151.862655216597</v>
+        <v>1155.243555281701</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -5816,10 +5616,10 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1151.862655216597</v>
+        <v>1155.243555281701</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1615.987126440999</v>
+        <v>1626.806006649332</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -5861,10 +5661,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1615.987126440999</v>
+        <v>1626.806006649332</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2072.617249545802</v>
+        <v>2087.493209832261</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -6119,10 +5919,10 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>720.1745637686945</v>
+        <v>750.1745637686945</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1071.854486441246</v>
+        <v>1101.854486441246</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -6160,10 +5960,10 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1071.854486441246</v>
+        <v>1101.854486441246</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1249.417280243849</v>
+        <v>1279.417280243849</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -6205,10 +6005,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1249.417280243849</v>
+        <v>1279.417280243849</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1675.693205685818</v>
+        <v>1735.693205685818</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -6250,10 +6050,10 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1675.693205685818</v>
+        <v>1735.693205685818</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1853.25599948842</v>
+        <v>1913.25599948842</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -6295,10 +6095,10 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1853.25599948842</v>
+        <v>1913.25599948842</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2223.975988485842</v>
+        <v>2283.975988485842</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -6463,10 +6263,10 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>720.1745637686945</v>
+        <v>750.1745637686945</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1121.737456577264</v>
+        <v>1151.737456577264</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -6504,10 +6304,10 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1121.737456577264</v>
+        <v>1151.737456577264</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1736.260297009333</v>
+        <v>1796.260297009333</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -6549,10 +6349,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1736.260297009333</v>
+        <v>1796.260297009333</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2168.773015664257</v>
+        <v>2228.773015664257</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -6590,10 +6390,10 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3780.646670135168</v>
+        <v>4147.853382995028</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4206.005617075611</v>
+        <v>4573.212329935472</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -6631,10 +6431,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4206.005617075611</v>
+        <v>4573.212329935472</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5123.688187595318</v>
+        <v>5634.894900455179</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -6676,10 +6476,10 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5123.688187595318</v>
+        <v>5634.894900455179</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5592.457548354121</v>
+        <v>6103.664261213982</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -6717,10 +6517,10 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3780.646670135168</v>
+        <v>4027.853382995028</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4193.562327568688</v>
+        <v>4440.769040428549</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -6758,10 +6558,10 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4193.562327568688</v>
+        <v>4440.769040428549</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4218.388168749222</v>
+        <v>4465.594881609083</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -6803,10 +6603,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4218.388168749222</v>
+        <v>4465.594881609083</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5148.830412339182</v>
+        <v>5396.037125199043</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -6848,10 +6648,10 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5148.830412339182</v>
+        <v>5396.037125199043</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5173.656253519715</v>
+        <v>5420.862966379576</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -6893,10 +6693,10 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5173.656253519715</v>
+        <v>5420.862966379576</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5604.607855370554</v>
+        <v>5851.814568230415</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -6934,10 +6734,10 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3780.646670135168</v>
+        <v>4027.853382995028</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4176.142495032499</v>
+        <v>4423.34920789236</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -6975,10 +6775,10 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4176.142495032499</v>
+        <v>4423.34920789236</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4393.36052789787</v>
+        <v>4640.567240757731</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -7020,10 +6820,10 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>4393.36052789787</v>
+        <v>4640.567240757731</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>4967.791415386984</v>
+        <v>5214.998128246845</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -7065,10 +6865,10 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>4967.791415386984</v>
+        <v>5214.998128246845</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>5185.009448252355</v>
+        <v>5432.216161112216</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -7110,10 +6910,10 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>5185.009448252355</v>
+        <v>5432.216161112216</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>5596.852561968046</v>
+        <v>5844.059274827907</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -7151,10 +6951,10 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>3780.646670135168</v>
+        <v>4057.853382995028</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>4177.087636293099</v>
+        <v>4454.294349152959</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -7192,10 +6992,10 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>4177.087636293099</v>
+        <v>4454.294349152959</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>4764.17320022275</v>
+        <v>5071.379913082611</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -7237,10 +7037,10 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>4764.17320022275</v>
+        <v>5071.379913082611</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>5190.22078340542</v>
+        <v>5497.427496265281</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -7278,10 +7078,10 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>7089.495449679997</v>
+        <v>7618.551855523426</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>7411.014863357202</v>
+        <v>7940.07126920063</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -7319,10 +7119,10 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>7411.014863357202</v>
+        <v>7940.07126920063</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>7913.753964372919</v>
+        <v>8472.810370216346</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -7364,10 +7164,10 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>7913.753964372919</v>
+        <v>8472.810370216346</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>8248.520770628247</v>
+        <v>8807.577176471677</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -7405,10 +7205,10 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>7089.495449679997</v>
+        <v>7618.551855523426</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>7403.689833549304</v>
+        <v>7932.746239392733</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -7446,10 +7246,10 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>7403.689833549304</v>
+        <v>7932.746239392733</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>7979.654275051361</v>
+        <v>8544.710680894788</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -7491,10 +7291,10 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>7979.654275051361</v>
+        <v>8544.710680894788</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>8310.401550156021</v>
+        <v>8875.457955999447</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -7532,10 +7332,10 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>7089.495449679997</v>
+        <v>7588.551855523426</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>7950.079314615133</v>
+        <v>8452.087718342676</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -7573,10 +7373,10 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>8790.401550156021</v>
+        <v>10393.46491263982</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>9805.828292735492</v>
+        <v>11480.8916552193</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -7614,10 +7414,10 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>8790.401550156021</v>
+        <v>10363.46491263982</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>9805.828292735492</v>
+        <v>11223.96984484465</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -7646,26 +7446,30 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>relay1</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>10623.33811138099</v>
+        <v>11223.96984484465</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>10953.59613786878</v>
+        <v>11829.52539446098</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>R-007</t>
+        </is>
+      </c>
       <c r="G51" s="3" t="n"/>
       <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
@@ -7687,30 +7491,26 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T017</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>relay0</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>10953.59613786878</v>
+        <v>11829.52539446098</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>11905.96279705516</v>
+        <v>12267.24432851611</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>R-006</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n"/>
       <c r="G52" s="3" t="n"/>
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
@@ -7741,10 +7541,10 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>11905.96279705516</v>
+        <v>13908.71877427553</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>12254.346248958</v>
+        <v>14226.89318381996</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -7773,26 +7573,30 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>relay0</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>10653.33811138099</v>
+        <v>14226.89318381996</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>11532.48373516954</v>
+        <v>14978.35080064794</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>R-008</t>
+        </is>
+      </c>
       <c r="G54" s="3" t="n"/>
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
@@ -7814,30 +7618,26 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>T019</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>relay1</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>11532.48373516954</v>
+        <v>14978.35080064794</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>11588.40580992071</v>
+        <v>15308.60882713574</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>R-007</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="n"/>
       <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
@@ -7864,25 +7664,21 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>relay0</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>11588.40580992071</v>
+        <v>13998.71877427553</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>12058.66866392462</v>
+        <v>14646.94100005273</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>R-006</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
@@ -7909,14 +7705,14 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>relay1</t>
+          <t>relay0</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>12058.66866392462</v>
+        <v>14646.94100005273</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>12115.34151312401</v>
+        <v>14684.99148216622</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -7925,7 +7721,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>R-007</t>
+          <t>R-008</t>
         </is>
       </c>
       <c r="G57" s="3" t="n"/>
@@ -7958,10 +7754,10 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>12115.34151312401</v>
+        <v>14684.99148216622</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>12547.98909708149</v>
+        <v>14723.04196427971</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -7990,26 +7786,30 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>relay0</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>14236.79245067192</v>
+        <v>14723.04196427971</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>14662.15139761237</v>
+        <v>15648.90348869317</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>R-008</t>
+        </is>
+      </c>
       <c r="G59" s="3" t="n"/>
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
@@ -8031,30 +7831,26 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>T020</t>
+          <t>T019</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>relay0</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>14662.15139761237</v>
+        <v>15648.90348869317</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>15723.83396813207</v>
+        <v>16042.3618201006</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>R-008</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="n"/>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
@@ -8085,10 +7881,10 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>15723.83396813207</v>
+        <v>17801.90745828352</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>16192.60332889088</v>
+        <v>18136.67426453885</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -8117,26 +7913,30 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>relay1</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>14176.79245067192</v>
+        <v>18136.67426453885</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>14543.19686545337</v>
+        <v>19526.83672789866</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>R-010</t>
+        </is>
+      </c>
       <c r="G62" s="3" t="n"/>
       <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
@@ -8158,30 +7958,26 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>T021</t>
+          <t>T020</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>relay0</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>14543.19686545337</v>
+        <v>19526.83672789866</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>14563.0575383978</v>
+        <v>19900.44889868078</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>R-008</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n"/>
       <c r="G63" s="3" t="n"/>
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
@@ -8208,25 +8004,21 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>relay1</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>14563.0575383978</v>
+        <v>17681.90745828352</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>15516.65893869783</v>
+        <v>18081.38763289026</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>R-009</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n"/>
       <c r="G64" s="3" t="n"/>
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
@@ -8257,10 +8049,10 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>15516.65893869783</v>
+        <v>18081.38763289026</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>15536.51961164226</v>
+        <v>18885.18610205106</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -8269,7 +8061,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>R-008</t>
+          <t>R-009</t>
         </is>
       </c>
       <c r="G65" s="3" t="n"/>
@@ -8302,10 +8094,10 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>15536.51961164226</v>
+        <v>18885.18610205106</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>15929.97794304969</v>
+        <v>19331.9009198818</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -8343,10 +8135,10 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>17899.79110963665</v>
+        <v>21457.11958033012</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>18248.88234719124</v>
+        <v>21853.53825139165</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -8384,10 +8176,10 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>18248.88234719124</v>
+        <v>21853.53825139165</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>18422.65677348353</v>
+        <v>22692.00346554742</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -8396,7 +8188,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>R-010</t>
+          <t>R-011</t>
         </is>
       </c>
       <c r="G68" s="3" t="n"/>
@@ -8425,25 +8217,21 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>relay1</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>18422.65677348353</v>
+        <v>22692.00346554742</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>19053.0601880088</v>
+        <v>23117.36241248787</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>R-011</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n"/>
       <c r="G69" s="3" t="n"/>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
@@ -8463,27 +8251,11 @@
       <c r="W69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>T022</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>19053.0601880088</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>19128.08041116627</v>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
+      <c r="A70" s="3" t="n"/>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
       <c r="F70" s="3" t="n"/>
       <c r="G70" s="3" t="n"/>
       <c r="H70" s="3" t="n"/>
@@ -8504,32 +8276,12 @@
       <c r="W70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>T022</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>relay1</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>19128.08041116627</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>19146.83546695563</v>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>R-011</t>
-        </is>
-      </c>
+      <c r="A71" s="3" t="n"/>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
       <c r="G71" s="3" t="n"/>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
@@ -8549,32 +8301,12 @@
       <c r="W71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>T022</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>relay0</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v>19146.83546695563</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>19841.05347311134</v>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>R-010</t>
-        </is>
-      </c>
+      <c r="A72" s="3" t="n"/>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
       <c r="G72" s="3" t="n"/>
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
@@ -8594,27 +8326,11 @@
       <c r="W72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>T022</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="n">
-        <v>19841.05347311134</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>20311.51098183112</v>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
+      <c r="A73" s="3" t="n"/>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n"/>
       <c r="G73" s="3" t="n"/>
       <c r="H73" s="3" t="n"/>
@@ -8635,27 +8351,11 @@
       <c r="W73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>21902.6721928587</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>22267.82702063642</v>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
+      <c r="A74" s="3" t="n"/>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n"/>
       <c r="G74" s="3" t="n"/>
       <c r="H74" s="3" t="n"/>
@@ -8676,32 +8376,12 @@
       <c r="W74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>relay1</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>22267.82702063642</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>22856.79579777212</v>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>R-013</t>
-        </is>
-      </c>
+      <c r="A75" s="3" t="n"/>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
       <c r="G75" s="3" t="n"/>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
@@ -8721,32 +8401,12 @@
       <c r="W75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>relay0</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>22856.79579777212</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>23261.92525658874</v>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>R-012</t>
-        </is>
-      </c>
+      <c r="A76" s="3" t="n"/>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
       <c r="G76" s="3" t="n"/>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
@@ -8766,32 +8426,12 @@
       <c r="W76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>relay1</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>23261.92525658874</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>23483.87874884199</v>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>R-013</t>
-        </is>
-      </c>
+      <c r="A77" s="3" t="n"/>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
       <c r="G77" s="3" t="n"/>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
@@ -8811,27 +8451,11 @@
       <c r="W77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>23483.87874884199</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>23918.71863560147</v>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
+      <c r="A78" s="3" t="n"/>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
       <c r="G78" s="3" t="n"/>
       <c r="H78" s="3" t="n"/>
@@ -8852,27 +8476,11 @@
       <c r="W78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>21902.6721928587</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>22264.14986759856</v>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
       <c r="G79" s="3" t="n"/>
       <c r="H79" s="3" t="n"/>
@@ -8892,292 +8500,8 @@
       <c r="V79" s="3" t="n"/>
       <c r="W79" s="3" t="n"/>
     </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>relay1</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>22264.14986759856</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>22303.970200346</v>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>R-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>relay0</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>22303.970200346</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>23165.5628241813</v>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>R-012</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="n">
-        <v>23165.5628241813</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>23598.07554283623</v>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="n">
-        <v>21872.6721928587</v>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>22272.15236746544</v>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>relay1</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="n">
-        <v>22272.15236746544</v>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>22677.11774591184</v>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>R-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>22677.11774591184</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>23094.69670876727</v>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>21992.6721928587</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>22632.5529845697</v>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>relay1</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="n">
-        <v>22632.5529845697</v>
-      </c>
-      <c r="D87" s="4" t="n">
-        <v>22707.55996651269</v>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>R-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="n">
-        <v>22707.55996651269</v>
-      </c>
-      <c r="D88" s="4" t="n">
-        <v>22726.31171199845</v>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>relay1</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>22726.31171199845</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>23296.08783078664</v>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>R-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="n">
-        <v>23296.08783078664</v>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>23650.72572590916</v>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F90"/>
+  <autoFilter ref="A1:F69"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9270,32 +8594,32 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>S001;S002;S003;S004;S005;S006;S007;S008;S009;S010;S011;S012;S014;S015</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
@@ -9312,32 +8636,32 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S002;S003;S004;S005;S006;S007;S008;S009;S010;S011;S012;S013;S014;S015</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
@@ -9354,32 +8678,32 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>S001;S003;S004;S005;S006;S007;S008;S009;S010;S011;S012;S014;S015</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
@@ -9396,32 +8720,32 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S002;S003;S004;S005;S006;S007;S008;S009;S010;S011;S012;S013;S015</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
@@ -9438,23 +8762,23 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0</v>
